--- a/data/trans_dic/P15D$urgencias-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P15D$urgencias-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuya consecuencia del último accidente fue, al menos, acudir a urgencias</t>
+          <t>Población cuya consecuencia del último accidente fue, al menos, acudir a urgencias (tasa de respuesta: 89,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>33,14; 73,68</t>
+          <t>32,11; 71,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>45,71; 68,52</t>
+          <t>46,13; 69,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36,53; 64,24</t>
+          <t>36,09; 63,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15,34; 41,14</t>
+          <t>15,54; 42,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>52,25; 79,94</t>
+          <t>52,3; 79,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,71; 61,72</t>
+          <t>42,19; 61,72</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,4; 67,95</t>
+          <t>44,28; 68,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>36,33; 52,23</t>
+          <t>36,61; 52,35</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>49,55; 72,68</t>
+          <t>49,16; 71,39</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>46,71; 61,63</t>
+          <t>47,22; 62,25</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>44,6; 63,88</t>
+          <t>45,27; 63,68</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>32,28; 46,01</t>
+          <t>32,04; 45,37</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>39,3; 61,56</t>
+          <t>38,34; 61,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>53,0; 68,11</t>
+          <t>53,82; 67,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55,61; 72,87</t>
+          <t>55,06; 73,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>59,98; 77,86</t>
+          <t>58,87; 76,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>42,77; 75,25</t>
+          <t>41,2; 76,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>45,42; 64,65</t>
+          <t>46,14; 65,26</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,53; 81,2</t>
+          <t>61,65; 81,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>45,69; 65,12</t>
+          <t>46,12; 64,66</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>43,66; 62,99</t>
+          <t>42,96; 63,09</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>53,38; 64,52</t>
+          <t>51,88; 64,76</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>60,82; 73,29</t>
+          <t>61,12; 73,73</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>56,34; 70,07</t>
+          <t>56,66; 69,87</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,63; 54,78</t>
+          <t>0,0; 50,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26,39; 65,23</t>
+          <t>25,38; 63,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>43,81; 80,64</t>
+          <t>43,64; 79,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>32,37; 72,52</t>
+          <t>31,31; 74,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>39,0; 92,67</t>
+          <t>41,47; 93,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>48,59; 83,44</t>
+          <t>46,34; 82,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>44,18; 81,21</t>
+          <t>45,78; 81,47</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>37,68; 65,53</t>
+          <t>35,6; 63,72</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>24,21; 62,77</t>
+          <t>24,92; 62,71</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>42,84; 71,04</t>
+          <t>43,13; 71,03</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>50,19; 75,86</t>
+          <t>48,51; 75,56</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>41,1; 65,1</t>
+          <t>39,19; 66,52</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>36,34; 55,33</t>
+          <t>37,74; 55,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>52,1; 63,86</t>
+          <t>52,42; 63,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>53,7; 68,04</t>
+          <t>54,04; 67,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51,27; 67,24</t>
+          <t>51,97; 66,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>54,64; 74,35</t>
+          <t>54,77; 75,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,01; 62,1</t>
+          <t>49,35; 62,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,09; 71,8</t>
+          <t>57,57; 71,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>44,94; 56,78</t>
+          <t>45,4; 56,57</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>47,39; 60,8</t>
+          <t>46,8; 61,38</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>52,75; 61,38</t>
+          <t>53,03; 61,74</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>57,77; 67,73</t>
+          <t>57,73; 68,16</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>49,81; 59,66</t>
+          <t>49,43; 59,4</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuya consecuencia del último accidente fue, al menos, acudir a urgencias</t>
+          <t>Población cuya consecuencia del último accidente fue, al menos, acudir a urgencias (tasa de respuesta: 89,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8343; 18548</t>
+          <t>8082; 17991</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>34196; 51256</t>
+          <t>34508; 51744</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16694; 29361</t>
+          <t>16493; 28927</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5462; 14648</t>
+          <t>5534; 15098</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>23786; 36394</t>
+          <t>23809; 36243</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>47783; 69044</t>
+          <t>47200; 69045</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33869; 50689</t>
+          <t>33034; 51190</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>28902; 41551</t>
+          <t>29122; 41644</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>35030; 51387</t>
+          <t>34757; 50471</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>87195; 115055</t>
+          <t>88143; 116209</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>53661; 76855</t>
+          <t>54462; 76607</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>37168; 52990</t>
+          <t>36899; 52244</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>30852; 48324</t>
+          <t>30101; 48247</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>96475; 123963</t>
+          <t>97966; 123313</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>67390; 88306</t>
+          <t>66724; 88571</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>78003; 101250</t>
+          <t>76557; 99692</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14988; 26371</t>
+          <t>14439; 26944</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>51641; 73513</t>
+          <t>52461; 74201</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>51239; 68746</t>
+          <t>52194; 69382</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>46584; 66399</t>
+          <t>47020; 65923</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>49576; 71527</t>
+          <t>48781; 71634</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>157842; 190795</t>
+          <t>153409; 191511</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>125200; 150859</t>
+          <t>125803; 151761</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>130718; 162552</t>
+          <t>131452; 162095</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1092; 10627</t>
+          <t>0; 9715</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6877; 16995</t>
+          <t>6613; 16673</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13491; 24835</t>
+          <t>13439; 24605</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10754; 24095</t>
+          <t>10404; 24886</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5162; 12266</t>
+          <t>5490; 12365</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13981; 24010</t>
+          <t>13335; 23807</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13698; 25181</t>
+          <t>14196; 25261</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>11629; 20228</t>
+          <t>10987; 19668</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7901; 20486</t>
+          <t>8134; 20466</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>23487; 38951</t>
+          <t>23650; 38944</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>31020; 46881</t>
+          <t>29979; 46701</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>26339; 41722</t>
+          <t>25115; 42632</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>44731; 68097</t>
+          <t>46445; 68865</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>147386; 180648</t>
+          <t>148278; 180372</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>106161; 134501</t>
+          <t>106821; 134113</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>101970; 133720</t>
+          <t>103356; 133233</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>51253; 69745</t>
+          <t>51379; 70627</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>124644; 157938</t>
+          <t>125526; 158211</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>108617; 136617</t>
+          <t>109543; 136873</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>95450; 120591</t>
+          <t>96429; 120146</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>102779; 131867</t>
+          <t>101500; 133121</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>283379; 329735</t>
+          <t>284897; 331661</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>224114; 262736</t>
+          <t>223968; 264416</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>204825; 245349</t>
+          <t>203297; 244297</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P15D$urgencias-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P15D$urgencias-Estudios-trans_dic.xlsx
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>39,21%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>32,11; 71,47</t>
+          <t>29,44; 71,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>46,13; 69,17</t>
+          <t>45,52; 69,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36,09; 63,29</t>
+          <t>35,61; 63,17</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15,54; 42,4</t>
+          <t>16,32; 41,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>52,3; 79,6</t>
+          <t>51,87; 79,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,19; 61,72</t>
+          <t>42,43; 60,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,28; 68,62</t>
+          <t>44,59; 69,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>36,61; 52,35</t>
+          <t>36,46; 52,53</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>49,16; 71,39</t>
+          <t>50,91; 72,79</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>47,22; 62,25</t>
+          <t>47,08; 61,93</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>45,27; 63,68</t>
+          <t>45,51; 63,3</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>32,04; 45,37</t>
+          <t>32,16; 46,16</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>70,28%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>64,44%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>38,34; 61,46</t>
+          <t>38,47; 61,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>53,82; 67,75</t>
+          <t>53,05; 68,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55,06; 73,09</t>
+          <t>55,64; 73,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>58,87; 76,66</t>
+          <t>61,86; 77,93</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>41,2; 76,89</t>
+          <t>43,06; 75,82</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>46,14; 65,26</t>
+          <t>46,19; 64,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>61,65; 81,96</t>
+          <t>62,69; 81,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>46,12; 64,66</t>
+          <t>47,43; 66,21</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>42,96; 63,09</t>
+          <t>43,87; 62,72</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51,88; 64,76</t>
+          <t>52,95; 64,72</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>61,12; 73,73</t>
+          <t>60,85; 74,22</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>56,66; 69,87</t>
+          <t>58,18; 71,01</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>55,46%</t>
+          <t>56,5%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>51,84%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>53,06%</t>
+          <t>54,37%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,07</t>
+          <t>5,66; 54,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25,38; 63,99</t>
+          <t>26,19; 64,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>43,64; 79,9</t>
+          <t>41,36; 80,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>31,31; 74,9</t>
+          <t>34,3; 75,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>41,47; 93,42</t>
+          <t>38,06; 92,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>46,34; 82,73</t>
+          <t>49,22; 83,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>45,78; 81,47</t>
+          <t>42,79; 80,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>35,6; 63,72</t>
+          <t>37,58; 65,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>24,92; 62,71</t>
+          <t>22,97; 62,14</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>43,13; 71,03</t>
+          <t>43,06; 71,6</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>48,51; 75,56</t>
+          <t>52,38; 76,74</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>39,19; 66,52</t>
+          <t>41,48; 66,21</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>59,21%</t>
+          <t>60,22%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>51,73%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>55,87%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>37,74; 55,95</t>
+          <t>37,08; 55,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>52,42; 63,76</t>
+          <t>51,96; 64,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>54,04; 67,84</t>
+          <t>53,9; 67,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51,97; 66,99</t>
+          <t>52,61; 67,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>54,77; 75,29</t>
+          <t>54,18; 73,78</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,35; 62,2</t>
+          <t>48,52; 60,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,57; 71,94</t>
+          <t>57,41; 71,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>45,4; 56,57</t>
+          <t>45,66; 57,88</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>46,8; 61,38</t>
+          <t>47,78; 61,13</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>53,03; 61,74</t>
+          <t>52,58; 61,58</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>57,73; 68,16</t>
+          <t>57,79; 67,54</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>49,43; 59,4</t>
+          <t>50,68; 60,41</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9617</t>
+          <t>10221</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>35013</t>
+          <t>37762</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>44630</t>
+          <t>47982</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8082; 17991</t>
+          <t>7412; 18004</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>34508; 51744</t>
+          <t>34056; 52139</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16493; 28927</t>
+          <t>16276; 28871</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5534; 15098</t>
+          <t>6176; 15606</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>23809; 36243</t>
+          <t>23614; 36272</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>47200; 69045</t>
+          <t>47466; 67893</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33034; 51190</t>
+          <t>33262; 51933</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>29122; 41644</t>
+          <t>30816; 44399</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>34757; 50471</t>
+          <t>35996; 51466</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>88143; 116209</t>
+          <t>87887; 115601</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>54462; 76607</t>
+          <t>54752; 76155</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>36899; 52244</t>
+          <t>39353; 56479</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>89713</t>
+          <t>98552</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>57033</t>
+          <t>63357</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>146746</t>
+          <t>161908</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>30101; 48247</t>
+          <t>30202; 48264</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>97966; 123313</t>
+          <t>96561; 124112</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>66724; 88571</t>
+          <t>67421; 88661</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>76557; 99692</t>
+          <t>86736; 109268</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14439; 26944</t>
+          <t>15087; 26568</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>52461; 74201</t>
+          <t>52525; 73480</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>52194; 69382</t>
+          <t>53074; 68974</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>47020; 65923</t>
+          <t>52660; 73512</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>48781; 71634</t>
+          <t>49818; 71216</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>153409; 191511</t>
+          <t>156596; 191377</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>125803; 151761</t>
+          <t>125246; 152765</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>131452; 162095</t>
+          <t>146177; 178408</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18427</t>
+          <t>23543</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15580</t>
+          <t>18269</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>34008</t>
+          <t>41812</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 9715</t>
+          <t>1099; 10655</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6613; 16673</t>
+          <t>6824; 16888</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13439; 24605</t>
+          <t>12736; 24832</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10404; 24886</t>
+          <t>14293; 31434</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5490; 12365</t>
+          <t>5037; 12250</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13335; 23807</t>
+          <t>14162; 23996</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14196; 25261</t>
+          <t>13266; 24879</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10987; 19668</t>
+          <t>13244; 22977</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8134; 20466</t>
+          <t>7495; 20279</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>23650; 38944</t>
+          <t>23609; 39260</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>29979; 46701</t>
+          <t>32373; 47425</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>25115; 42632</t>
+          <t>31901; 50919</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>117758</t>
+          <t>132315</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>107626</t>
+          <t>119388</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>225384</t>
+          <t>251703</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>46445; 68865</t>
+          <t>45632; 68392</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>148278; 180372</t>
+          <t>146995; 183600</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>106821; 134113</t>
+          <t>106540; 132787</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>103356; 133233</t>
+          <t>115598; 147944</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>51379; 70627</t>
+          <t>50824; 69211</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>125526; 158211</t>
+          <t>123411; 153519</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>109543; 136873</t>
+          <t>109229; 136949</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>96429; 120146</t>
+          <t>105374; 133569</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>101500; 133121</t>
+          <t>103625; 132591</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>284897; 331661</t>
+          <t>282453; 330834</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>223968; 264416</t>
+          <t>224181; 262007</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>203297; 244297</t>
+          <t>228309; 272153</t>
         </is>
       </c>
     </row>
